--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Chen 1998.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Chen 1998.xlsx
@@ -9,7 +9,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoSCoW_эксперт 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoSCoW_эксперт 2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoSCoW_эксперт 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Четкий MoSCoW_коллектив" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица_взаимосвязей_FR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Четкий MoSCoW_расчеты" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Четкий MoSCoW_итоги" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +45,10 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -160,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -189,8 +195,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -536,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -588,12 +614,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -644,7 +670,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -661,17 +687,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -688,12 +714,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -715,7 +741,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -732,7 +758,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -749,12 +775,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -771,7 +797,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -781,7 +807,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -798,12 +824,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -815,17 +841,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -842,12 +868,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
           <t>Mo</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
         </is>
       </c>
     </row>
@@ -867,7 +893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -919,12 +945,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
           <t>Mo</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
         </is>
       </c>
     </row>
@@ -970,12 +996,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -992,17 +1018,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1045,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1067,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1089,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1080,7 +1106,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1102,17 +1128,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1155,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1172,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1199,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
           <t>Mo</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1245,12 +1271,12 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1301,12 +1327,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1323,17 +1349,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Co</t>
-        </is>
-      </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -1345,17 +1371,17 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1403,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -1389,17 +1415,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Co</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1437,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
           <t>Co</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1443,7 +1469,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1455,17 +1481,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Co</t>
-        </is>
-      </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -1477,17 +1503,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1525,17 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Mo</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
         </is>
       </c>
     </row>
@@ -1529,31 +1555,494 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F153"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Матрица взаимосвязанности функциональных требований</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E161"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Пример применения MoSCoW (четкая модель) + КПР (четкий аналог Chen 1998)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>Таблица 1. Удельные веса экспертов</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Четкий MoSCoW_расчеты</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>1) Веса экспертов</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Эксперт</t>
@@ -1570,1796 +2059,2420 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Эксперт 1</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
         <v>0.75</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="14" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Эксперт 2</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
         <v>0.75</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="14" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Эксперт 3</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14" t="n">
         <v>0.4</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>SUM</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="18" t="n">
         <v>2.5</v>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Нормализация параметров (для матриц согласия и C(Ei))</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="C8" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>2) Параметры алгоритма и нормализации</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Нормализованные данные</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Ненормализованные
+данные</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>m = max(PFR) по всем экспертам и FR</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>15.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Параметр</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>Нормализованные данные</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Ненормализованные данные</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="B12" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="C12" s="19" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>y1</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="14" t="n">
         <v>0.6</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="14" t="n">
         <v>0.9</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>y2</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="14" t="n">
         <v>0.4</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="14" t="n">
         <v>0.6</v>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Таблица 2. Индивидуальные экспертные рейтинги FR по MoSCoW (PFR_raw)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>3) Индивидуальные оценки PFR_raw по экспертам</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>PFR_raw Эксперт 1</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>PFR_raw Эксперт 2</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>PFR_raw Эксперт 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>14.15</v>
-      </c>
-      <c r="C18" t="n">
-        <v>12.425</v>
-      </c>
-      <c r="D18" t="n">
-        <v>11.625</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="B19" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>6.600000000000001</v>
-      </c>
-      <c r="C19" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="D19" t="n">
-        <v>5.775</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="B20" s="14" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>15.095</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="C20" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="D20" t="n">
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="B21" s="14" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>7.095000000000001</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>12.45</v>
-      </c>
-      <c r="C21" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>8.275</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="B22" s="14" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>18.78</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="C22" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="D22" t="n">
-        <v>9.125</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="B23" s="14" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>13.42</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="C23" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>6.600000000000001</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="B24" s="14" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>8.91</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="C24" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>8.275</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="B25" s="14" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>10.78</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>12.45</v>
-      </c>
-      <c r="C25" t="n">
-        <v>12.425</v>
-      </c>
-      <c r="D25" t="n">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="B26" s="14" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>16.06</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="C26" t="n">
-        <v>13.275</v>
-      </c>
-      <c r="D26" t="n">
-        <v>9.125</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="B27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>1.815</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>8.275</v>
-      </c>
-      <c r="C27" t="n">
-        <v>13.275</v>
-      </c>
-      <c r="D27" t="n">
-        <v>10.775</v>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>Таблица 3. Нормализованные оценки PFR_norm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="B28" s="14" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>14.27</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>4) Нормализованные оценки PFR_norm по экспертам</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1"/>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>PFR_norm Эксперт 1</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>PFR_norm Эксперт 2</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>PFR_norm Эксперт 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>0.8984126984126984</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.788888888888889</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.7380952380952381</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="B33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>0.4190476190476191</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.5238095238095238</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.3666666666666667</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="B34" s="14" t="n">
+        <v>0.5533333333333333</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>0.6289583333333334</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>0.6285714285714286</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.7365079365079364</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="B35" s="14" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>0.295625</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>0.2291666666666667</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>0.7904761904761906</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.8952380952380952</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.5253968253968254</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="B36" s="14" t="n">
+        <v>0.8866666666666667</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>0.7825000000000001</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>0.6825396825396826</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.5793650793650794</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="B37" s="14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>0.5912500000000001</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>0.5591666666666667</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0.6857142857142857</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.8952380952380952</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.4190476190476191</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="B38" s="14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>0.37125</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>0.6857142857142857</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.8952380952380952</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.5253968253968254</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="B39" s="14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>0.4491666666666667</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>0.4491666666666667</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>0.7904761904761904</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.788888888888889</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.6857142857142857</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="B40" s="14" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>0.6691666666666668</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>0.6691666666666668</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>0.6825396825396826</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0.8428571428571429</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.5793650793650794</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="B41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>0.07562500000000001</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>0.07562500000000001</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>0.5253968253968254</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.8428571428571429</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.6841269841269841</v>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>Матрицы согласия AM(Sij) по PFR_norm</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="B42" s="14" t="n">
+        <v>0.5533333333333333</v>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>0.5945833333333334</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>0.5945833333333334</v>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1"/>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>5) Матрицы согласия AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>Матрицы согласия по нормализованным оценкам</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1"/>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0.8904761904761905</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.8396825396825397</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="n">
-        <v>0.8904761904761905</v>
-      </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.9492063492063492</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="n">
-        <v>0.8396825396825397</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.9492063492063492</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="13" t="n"/>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="14" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="C50" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="C51" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1"/>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.8952380952380952</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.9476190476190476</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="n">
-        <v>0.8952380952380952</v>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.8428571428571429</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="n">
-        <v>0.9476190476190476</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.8428571428571429</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" s="12" t="inlineStr">
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="13" t="n"/>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="14" t="n">
+        <v>0.9908333333333333</v>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>0.9243749999999999</v>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="n">
+        <v>0.9908333333333333</v>
+      </c>
+      <c r="C56" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>0.9335416666666666</v>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="n">
+        <v>0.9243749999999999</v>
+      </c>
+      <c r="C57" s="14" t="n">
+        <v>0.9335416666666666</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1"/>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.6285714285714286</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.8920634920634921</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="n">
-        <v>0.6285714285714286</v>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.7365079365079364</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="n">
-        <v>0.8920634920634921</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0.7365079365079364</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" s="12" t="inlineStr">
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="13" t="n"/>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="14" t="n">
+        <v>0.9243749999999999</v>
+      </c>
+      <c r="D61" s="14" t="n">
+        <v>0.9908333333333333</v>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="n">
+        <v>0.9243749999999999</v>
+      </c>
+      <c r="C62" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="14" t="n">
+        <v>0.9335416666666666</v>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="n">
+        <v>0.9908333333333333</v>
+      </c>
+      <c r="C63" s="14" t="n">
+        <v>0.9335416666666666</v>
+      </c>
+      <c r="D63" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1"/>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="17" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.8952380952380954</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.7349206349206349</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" t="n">
-        <v>0.8952380952380954</v>
-      </c>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0.6301587301587303</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" t="n">
-        <v>0.7349206349206349</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.6301587301587303</v>
-      </c>
-      <c r="D59" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="13" t="n"/>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="14" t="n">
+        <v>0.9908333333333333</v>
+      </c>
+      <c r="D67" s="14" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="n">
+        <v>0.9908333333333333</v>
+      </c>
+      <c r="C68" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="14" t="n">
+        <v>0.8866666666666667</v>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="C69" s="14" t="n">
+        <v>0.8866666666666667</v>
+      </c>
+      <c r="D69" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1"/>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="17" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0.6825396825396826</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0.8968253968253969</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" t="n">
-        <v>0.6825396825396826</v>
-      </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0.5793650793650794</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" t="n">
-        <v>0.8968253968253969</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0.5793650793650794</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="13" t="n"/>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" s="14" t="n">
+        <v>0.95875</v>
+      </c>
+      <c r="D73" s="14" t="n">
+        <v>0.9908333333333333</v>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="n">
+        <v>0.95875</v>
+      </c>
+      <c r="C74" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="14" t="n">
+        <v>0.9679166666666666</v>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="n">
+        <v>0.9908333333333333</v>
+      </c>
+      <c r="C75" s="14" t="n">
+        <v>0.9679166666666666</v>
+      </c>
+      <c r="D75" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1"/>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="17" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0.7904761904761906</v>
-      </c>
-      <c r="D65" t="n">
-        <v>0.7333333333333334</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" t="n">
-        <v>0.7904761904761906</v>
-      </c>
-      <c r="C66" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" t="n">
-        <v>0.5238095238095239</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" t="n">
-        <v>0.7333333333333334</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0.5238095238095239</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="13" t="n"/>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="14" t="n">
+        <v>0.95875</v>
+      </c>
+      <c r="D79" s="14" t="n">
+        <v>0.95875</v>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="n">
+        <v>0.95875</v>
+      </c>
+      <c r="C80" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="n">
+        <v>0.95875</v>
+      </c>
+      <c r="C81" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1"/>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="17" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0.7904761904761906</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0.8396825396825397</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" t="n">
-        <v>0.7904761904761906</v>
-      </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" t="n">
-        <v>0.6301587301587303</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" t="n">
-        <v>0.8396825396825397</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0.6301587301587303</v>
-      </c>
-      <c r="D71" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" s="12" t="inlineStr">
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="13" t="n"/>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C84" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="14" t="n">
+        <v>0.9908333333333332</v>
+      </c>
+      <c r="D85" s="14" t="n">
+        <v>0.9908333333333332</v>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="n">
+        <v>0.9908333333333332</v>
+      </c>
+      <c r="C86" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="n">
+        <v>0.9908333333333332</v>
+      </c>
+      <c r="C87" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1"/>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="17" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>1</v>
-      </c>
-      <c r="C73" t="n">
-        <v>0.9984126984126985</v>
-      </c>
-      <c r="D73" t="n">
-        <v>0.8952380952380953</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" t="n">
-        <v>0.9984126984126985</v>
-      </c>
-      <c r="C74" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" t="n">
-        <v>0.8968253968253967</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" t="n">
-        <v>0.8952380952380953</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0.8968253968253967</v>
-      </c>
-      <c r="D75" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76"/>
-    <row r="77">
-      <c r="A77" s="12" t="inlineStr">
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="13" t="n"/>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D90" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B91" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" s="14" t="n">
+        <v>0.9908333333333332</v>
+      </c>
+      <c r="D91" s="14" t="n">
+        <v>0.9908333333333332</v>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="n">
+        <v>0.9908333333333332</v>
+      </c>
+      <c r="C92" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B93" s="14" t="n">
+        <v>0.9908333333333332</v>
+      </c>
+      <c r="C93" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1"/>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="17" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>1</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0.8396825396825397</v>
-      </c>
-      <c r="D77" t="n">
-        <v>0.8968253968253969</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" t="n">
-        <v>0.8396825396825397</v>
-      </c>
-      <c r="C78" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" t="n">
-        <v>0.7365079365079366</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" t="n">
-        <v>0.8968253968253969</v>
-      </c>
-      <c r="C79" t="n">
-        <v>0.7365079365079366</v>
-      </c>
-      <c r="D79" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80"/>
-    <row r="81">
-      <c r="A81" s="12" t="inlineStr">
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="13" t="n"/>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B97" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" s="14" t="n">
+        <v>0.9243749999999999</v>
+      </c>
+      <c r="D97" s="14" t="n">
+        <v>0.9243749999999999</v>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="n">
+        <v>0.9243749999999999</v>
+      </c>
+      <c r="C98" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B99" s="14" t="n">
+        <v>0.9243749999999999</v>
+      </c>
+      <c r="C99" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1"/>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="17" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>1</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0.6825396825396826</v>
-      </c>
-      <c r="D81" t="n">
-        <v>0.8412698412698413</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" t="n">
-        <v>0.6825396825396826</v>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="n">
-        <v>0.8412698412698413</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" t="n">
-        <v>0.8412698412698413</v>
-      </c>
-      <c r="C83" t="n">
-        <v>0.8412698412698413</v>
-      </c>
-      <c r="D83" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86">
-      <c r="A86" s="13" t="inlineStr">
-        <is>
-          <t>Таблица 4. Средняя степень согласия эксперта A(Ei)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="13" t="inlineStr">
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="13" t="n"/>
+      <c r="B102" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C102" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D102" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B103" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" s="14" t="n">
+        <v>0.95875</v>
+      </c>
+      <c r="D103" s="14" t="n">
+        <v>0.95875</v>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="n">
+        <v>0.95875</v>
+      </c>
+      <c r="C104" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B105" s="14" t="n">
+        <v>0.95875</v>
+      </c>
+      <c r="C105" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1"/>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="15" t="inlineStr">
+        <is>
+          <t>6) Средняя степень согласия эксперта A(Ei)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1"/>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="13" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="B87" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 1</t>
-        </is>
-      </c>
-      <c r="C87" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 2</t>
-        </is>
-      </c>
-      <c r="D87" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="B109" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C109" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D109" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="19" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B88" t="n">
-        <v>0.8650793650793651</v>
-      </c>
-      <c r="C88" t="n">
-        <v>0.9198412698412699</v>
-      </c>
-      <c r="D88" t="n">
-        <v>0.8944444444444444</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="B110" s="14" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="C110" s="14" t="n">
+        <v>0.9479166666666667</v>
+      </c>
+      <c r="D110" s="14" t="n">
+        <v>0.9479166666666667</v>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="19" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>0.9214285714285714</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0.8690476190476191</v>
-      </c>
-      <c r="D89" t="n">
-        <v>0.8952380952380952</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="B111" s="14" t="n">
+        <v>0.9576041666666666</v>
+      </c>
+      <c r="C111" s="14" t="n">
+        <v>0.9621875</v>
+      </c>
+      <c r="D111" s="14" t="n">
+        <v>0.9289583333333333</v>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="19" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B90" t="n">
-        <v>0.7603174603174603</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0.6825396825396826</v>
-      </c>
-      <c r="D90" t="n">
-        <v>0.8142857142857143</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="B112" s="14" t="n">
+        <v>0.9576041666666666</v>
+      </c>
+      <c r="C112" s="14" t="n">
+        <v>0.9289583333333333</v>
+      </c>
+      <c r="D112" s="14" t="n">
+        <v>0.9621875</v>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="19" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B91" t="n">
-        <v>0.8150793650793651</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0.7626984126984129</v>
-      </c>
-      <c r="D91" t="n">
-        <v>0.6825396825396826</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="B113" s="14" t="n">
+        <v>0.9433333333333334</v>
+      </c>
+      <c r="C113" s="14" t="n">
+        <v>0.93875</v>
+      </c>
+      <c r="D113" s="14" t="n">
+        <v>0.8912500000000001</v>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="19" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>0.7896825396825398</v>
-      </c>
-      <c r="C92" t="n">
-        <v>0.6309523809523809</v>
-      </c>
-      <c r="D92" t="n">
-        <v>0.7380952380952381</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="B114" s="14" t="n">
+        <v>0.9747916666666667</v>
+      </c>
+      <c r="C114" s="14" t="n">
+        <v>0.9633333333333334</v>
+      </c>
+      <c r="D114" s="14" t="n">
+        <v>0.979375</v>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="19" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B93" t="n">
-        <v>0.761904761904762</v>
-      </c>
-      <c r="C93" t="n">
-        <v>0.6571428571428573</v>
-      </c>
-      <c r="D93" t="n">
-        <v>0.6285714285714287</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="B115" s="14" t="n">
+        <v>0.95875</v>
+      </c>
+      <c r="C115" s="14" t="n">
+        <v>0.979375</v>
+      </c>
+      <c r="D115" s="14" t="n">
+        <v>0.979375</v>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="19" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B94" t="n">
-        <v>0.8150793650793651</v>
-      </c>
-      <c r="C94" t="n">
-        <v>0.7103174603174605</v>
-      </c>
-      <c r="D94" t="n">
-        <v>0.734920634920635</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="B116" s="14" t="n">
+        <v>0.9908333333333332</v>
+      </c>
+      <c r="C116" s="14" t="n">
+        <v>0.9954166666666666</v>
+      </c>
+      <c r="D116" s="14" t="n">
+        <v>0.9954166666666666</v>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="19" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B95" t="n">
-        <v>0.9468253968253969</v>
-      </c>
-      <c r="C95" t="n">
-        <v>0.9476190476190476</v>
-      </c>
-      <c r="D95" t="n">
-        <v>0.896031746031746</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="B117" s="14" t="n">
+        <v>0.9908333333333332</v>
+      </c>
+      <c r="C117" s="14" t="n">
+        <v>0.9954166666666666</v>
+      </c>
+      <c r="D117" s="14" t="n">
+        <v>0.9954166666666666</v>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="19" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>0.8682539682539683</v>
-      </c>
-      <c r="C96" t="n">
-        <v>0.7880952380952382</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0.8166666666666667</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="B118" s="14" t="n">
+        <v>0.9243749999999999</v>
+      </c>
+      <c r="C118" s="14" t="n">
+        <v>0.9621875</v>
+      </c>
+      <c r="D118" s="14" t="n">
+        <v>0.9621875</v>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="19" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B97" t="n">
-        <v>0.7619047619047619</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.7619047619047619</v>
-      </c>
-      <c r="D97" t="n">
-        <v>0.8412698412698413</v>
-      </c>
-    </row>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100">
-      <c r="A100" s="13" t="inlineStr">
-        <is>
-          <t>Таблица 5. Относительная степень согласия эксперта RA(Ei)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="13" t="inlineStr">
+      <c r="B119" s="14" t="n">
+        <v>0.95875</v>
+      </c>
+      <c r="C119" s="14" t="n">
+        <v>0.979375</v>
+      </c>
+      <c r="D119" s="14" t="n">
+        <v>0.979375</v>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1"/>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="15" t="inlineStr">
+        <is>
+          <t>7) Относительная степень согласия эксперта RA(Ei)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1"/>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="13" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="B101" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 1</t>
-        </is>
-      </c>
-      <c r="C101" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 2</t>
-        </is>
-      </c>
-      <c r="D101" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="B123" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C123" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D123" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="19" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B102" t="n">
-        <v>0.322867298578199</v>
-      </c>
-      <c r="C102" t="n">
-        <v>0.3433056872037915</v>
-      </c>
-      <c r="D102" t="n">
-        <v>0.3338270142180094</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="B124" s="14" t="n">
+        <v>0.3208955223880597</v>
+      </c>
+      <c r="C124" s="14" t="n">
+        <v>0.3395522388059701</v>
+      </c>
+      <c r="D124" s="14" t="n">
+        <v>0.3395522388059701</v>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="19" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B103" t="n">
-        <v>0.3430851063829787</v>
-      </c>
-      <c r="C103" t="n">
-        <v>0.323581560283688</v>
-      </c>
-      <c r="D103" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="B125" s="14" t="n">
+        <v>0.3361488957144946</v>
+      </c>
+      <c r="C125" s="14" t="n">
+        <v>0.3377577885037297</v>
+      </c>
+      <c r="D125" s="14" t="n">
+        <v>0.3260933157817756</v>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="19" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B104" t="n">
-        <v>0.3368495077355837</v>
-      </c>
-      <c r="C104" t="n">
-        <v>0.3023909985935302</v>
-      </c>
-      <c r="D104" t="n">
-        <v>0.3607594936708861</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="B126" s="14" t="n">
+        <v>0.3361488957144946</v>
+      </c>
+      <c r="C126" s="14" t="n">
+        <v>0.3260933157817756</v>
+      </c>
+      <c r="D126" s="14" t="n">
+        <v>0.3377577885037297</v>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="19" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B105" t="n">
-        <v>0.3606039325842696</v>
-      </c>
-      <c r="C105" t="n">
-        <v>0.337429775280899</v>
-      </c>
-      <c r="D105" t="n">
-        <v>0.3019662921348314</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="B127" s="14" t="n">
+        <v>0.3401442307692308</v>
+      </c>
+      <c r="C127" s="14" t="n">
+        <v>0.3384915865384615</v>
+      </c>
+      <c r="D127" s="14" t="n">
+        <v>0.3213641826923077</v>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="19" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B106" t="n">
-        <v>0.3658088235294117</v>
-      </c>
-      <c r="C106" t="n">
-        <v>0.2922794117647058</v>
-      </c>
-      <c r="D106" t="n">
-        <v>0.3419117647058823</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="B128" s="14" t="n">
+        <v>0.3341188231933733</v>
+      </c>
+      <c r="C128" s="14" t="n">
+        <v>0.3301913738931734</v>
+      </c>
+      <c r="D128" s="14" t="n">
+        <v>0.3356898029134533</v>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="19" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B107" t="n">
-        <v>0.3720930232558139</v>
-      </c>
-      <c r="C107" t="n">
-        <v>0.3209302325581396</v>
-      </c>
-      <c r="D107" t="n">
-        <v>0.3069767441860465</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="B129" s="14" t="n">
+        <v>0.3286203941730934</v>
+      </c>
+      <c r="C129" s="14" t="n">
+        <v>0.3356898029134533</v>
+      </c>
+      <c r="D129" s="14" t="n">
+        <v>0.3356898029134533</v>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="19" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B108" t="n">
-        <v>0.3606039325842696</v>
-      </c>
-      <c r="C108" t="n">
-        <v>0.3142556179775282</v>
-      </c>
-      <c r="D108" t="n">
-        <v>0.3251404494382023</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="B130" s="14" t="n">
+        <v>0.3323085522638345</v>
+      </c>
+      <c r="C130" s="14" t="n">
+        <v>0.3338457238680828</v>
+      </c>
+      <c r="D130" s="14" t="n">
+        <v>0.3338457238680828</v>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="19" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B109" t="n">
-        <v>0.3393060295790672</v>
-      </c>
-      <c r="C109" t="n">
-        <v>0.3395904436860068</v>
-      </c>
-      <c r="D109" t="n">
-        <v>0.321103526734926</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="B131" s="14" t="n">
+        <v>0.3323085522638345</v>
+      </c>
+      <c r="C131" s="14" t="n">
+        <v>0.3338457238680828</v>
+      </c>
+      <c r="D131" s="14" t="n">
+        <v>0.3338457238680828</v>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="19" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B110" t="n">
-        <v>0.3510911424903723</v>
-      </c>
-      <c r="C110" t="n">
-        <v>0.3186777920410783</v>
-      </c>
-      <c r="D110" t="n">
-        <v>0.3302310654685494</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="B132" s="14" t="n">
+        <v>0.3244844229925406</v>
+      </c>
+      <c r="C132" s="14" t="n">
+        <v>0.3377577885037297</v>
+      </c>
+      <c r="D132" s="14" t="n">
+        <v>0.3377577885037297</v>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="19" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B111" t="n">
-        <v>0.3221476510067114</v>
-      </c>
-      <c r="C111" t="n">
-        <v>0.3221476510067114</v>
-      </c>
-      <c r="D111" t="n">
-        <v>0.3557046979865772</v>
-      </c>
-    </row>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114">
-      <c r="A114" s="13" t="inlineStr">
-        <is>
-          <t>Таблица 6. Коэффициент степени консенсуса эксперта C(Ei)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="13" t="inlineStr">
+      <c r="B133" s="14" t="n">
+        <v>0.3286203941730934</v>
+      </c>
+      <c r="C133" s="14" t="n">
+        <v>0.3356898029134533</v>
+      </c>
+      <c r="D133" s="14" t="n">
+        <v>0.3356898029134533</v>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1"/>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="15" t="inlineStr">
+        <is>
+          <t>8) Коэффициент степени консенсуса эксперта C(Ei)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1"/>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="13" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="B115" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 1</t>
-        </is>
-      </c>
-      <c r="C115" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 2</t>
-        </is>
-      </c>
-      <c r="D115" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="B137" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C137" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D137" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="19" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B116" t="n">
-        <v>0.3091469194312796</v>
-      </c>
-      <c r="C116" t="n">
-        <v>0.3173222748815165</v>
-      </c>
-      <c r="D116" t="n">
-        <v>0.3735308056872038</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="B138" s="14" t="n">
+        <v>0.3083582089552239</v>
+      </c>
+      <c r="C138" s="14" t="n">
+        <v>0.315820895522388</v>
+      </c>
+      <c r="D138" s="14" t="n">
+        <v>0.3758208955223881</v>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="19" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B117" t="n">
-        <v>0.3172340425531915</v>
-      </c>
-      <c r="C117" t="n">
-        <v>0.3094326241134752</v>
-      </c>
-      <c r="D117" t="n">
-        <v>0.3733333333333333</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="B139" s="14" t="n">
+        <v>0.3144595582857979</v>
+      </c>
+      <c r="C139" s="14" t="n">
+        <v>0.3151031154014919</v>
+      </c>
+      <c r="D139" s="14" t="n">
+        <v>0.3704373263127102</v>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="19" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B118" t="n">
-        <v>0.3147398030942334</v>
-      </c>
-      <c r="C118" t="n">
-        <v>0.3009563994374121</v>
-      </c>
-      <c r="D118" t="n">
-        <v>0.3843037974683544</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="B140" s="14" t="n">
+        <v>0.3144595582857979</v>
+      </c>
+      <c r="C140" s="14" t="n">
+        <v>0.3104373263127103</v>
+      </c>
+      <c r="D140" s="14" t="n">
+        <v>0.3751031154014919</v>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="19" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B119" t="n">
-        <v>0.3242415730337078</v>
-      </c>
-      <c r="C119" t="n">
-        <v>0.3149719101123596</v>
-      </c>
-      <c r="D119" t="n">
-        <v>0.3607865168539326</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="B141" s="14" t="n">
+        <v>0.3160576923076923</v>
+      </c>
+      <c r="C141" s="14" t="n">
+        <v>0.3153966346153846</v>
+      </c>
+      <c r="D141" s="14" t="n">
+        <v>0.3685456730769231</v>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="19" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B120" t="n">
-        <v>0.3263235294117647</v>
-      </c>
-      <c r="C120" t="n">
-        <v>0.2969117647058823</v>
-      </c>
-      <c r="D120" t="n">
-        <v>0.3767647058823529</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="B142" s="14" t="n">
+        <v>0.3136475292773493</v>
+      </c>
+      <c r="C142" s="14" t="n">
+        <v>0.3120765495572693</v>
+      </c>
+      <c r="D142" s="14" t="n">
+        <v>0.3742759211653813</v>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="19" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>0.3288372093023256</v>
-      </c>
-      <c r="C121" t="n">
-        <v>0.3083720930232558</v>
-      </c>
-      <c r="D121" t="n">
-        <v>0.3627906976744186</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="B143" s="14" t="n">
+        <v>0.3114481576692373</v>
+      </c>
+      <c r="C143" s="14" t="n">
+        <v>0.3142759211653813</v>
+      </c>
+      <c r="D143" s="14" t="n">
+        <v>0.3742759211653813</v>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="19" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B122" t="n">
-        <v>0.3242415730337078</v>
-      </c>
-      <c r="C122" t="n">
-        <v>0.3057022471910112</v>
-      </c>
-      <c r="D122" t="n">
-        <v>0.3700561797752809</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="B144" s="14" t="n">
+        <v>0.3129234209055338</v>
+      </c>
+      <c r="C144" s="14" t="n">
+        <v>0.3135382895472331</v>
+      </c>
+      <c r="D144" s="14" t="n">
+        <v>0.3735382895472331</v>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="19" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B123" t="n">
-        <v>0.3157224118316269</v>
-      </c>
-      <c r="C123" t="n">
-        <v>0.3158361774744027</v>
-      </c>
-      <c r="D123" t="n">
-        <v>0.3684414106939704</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="B145" s="14" t="n">
+        <v>0.3129234209055338</v>
+      </c>
+      <c r="C145" s="14" t="n">
+        <v>0.3135382895472331</v>
+      </c>
+      <c r="D145" s="14" t="n">
+        <v>0.3735382895472331</v>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="19" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B124" t="n">
-        <v>0.3204364569961489</v>
-      </c>
-      <c r="C124" t="n">
-        <v>0.3074711168164313</v>
-      </c>
-      <c r="D124" t="n">
-        <v>0.3720924261874198</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="B146" s="14" t="n">
+        <v>0.3097937691970162</v>
+      </c>
+      <c r="C146" s="14" t="n">
+        <v>0.3151031154014919</v>
+      </c>
+      <c r="D146" s="14" t="n">
+        <v>0.3751031154014919</v>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="19" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B125" t="n">
-        <v>0.3088590604026845</v>
-      </c>
-      <c r="C125" t="n">
-        <v>0.3088590604026845</v>
-      </c>
-      <c r="D125" t="n">
-        <v>0.3822818791946309</v>
-      </c>
-    </row>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128">
-      <c r="A128" s="13" t="inlineStr">
-        <is>
-          <t>Таблица 7. Коллективный рейтинг</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="13" t="inlineStr">
+      <c r="B147" s="14" t="n">
+        <v>0.3114481576692373</v>
+      </c>
+      <c r="C147" s="14" t="n">
+        <v>0.3142759211653813</v>
+      </c>
+      <c r="D147" s="14" t="n">
+        <v>0.3742759211653813</v>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1"/>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="15" t="inlineStr">
+        <is>
+          <t>9) Вклады экспертов в коллективный рейтинг</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1"/>
+    <row r="151" ht="36" customHeight="1">
+      <c r="A151" s="13" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="B129" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 1: PFR_raw*C(Ei)</t>
-        </is>
-      </c>
-      <c r="C129" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 2: PFR_raw*C(Ei)</t>
-        </is>
-      </c>
-      <c r="D129" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 3: PFR_raw*C(Ei)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="B151" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1: PFR_raw*C(Ei)</t>
+        </is>
+      </c>
+      <c r="C151" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2: PFR_raw*C(Ei)</t>
+        </is>
+      </c>
+      <c r="D151" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3: PFR_raw*C(Ei)</t>
+        </is>
+      </c>
+      <c r="E151" s="13" t="inlineStr">
+        <is>
+          <t>Коллективная оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="19" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B130" t="n">
-        <v>4.374428909952607</v>
-      </c>
-      <c r="C130" t="n">
-        <v>3.942729265402843</v>
-      </c>
-      <c r="D130" t="n">
-        <v>4.342295616113744</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="B152" s="14" t="n">
+        <v>7.400597014925372</v>
+      </c>
+      <c r="C152" s="14" t="n">
+        <v>6.790149253731342</v>
+      </c>
+      <c r="D152" s="14" t="n">
+        <v>8.080149253731344</v>
+      </c>
+      <c r="E152" s="14" t="n">
+        <v>22.27089552238806</v>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1">
+      <c r="A153" s="19" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B131" t="n">
-        <v>2.093744680851064</v>
-      </c>
-      <c r="C131" t="n">
-        <v>2.55281914893617</v>
-      </c>
-      <c r="D131" t="n">
-        <v>2.156</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="B153" s="14" t="n">
+        <v>4.176022934035396</v>
+      </c>
+      <c r="C153" s="14" t="n">
+        <v>4.25389205792014</v>
+      </c>
+      <c r="D153" s="14" t="n">
+        <v>5.591751440690361</v>
+      </c>
+      <c r="E153" s="14" t="n">
+        <v>14.0216664326459</v>
+      </c>
+    </row>
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="19" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B132" t="n">
-        <v>3.115924050632911</v>
-      </c>
-      <c r="C132" t="n">
-        <v>4.740063291139241</v>
-      </c>
-      <c r="D132" t="n">
-        <v>4.457924050632911</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="B154" s="14" t="n">
+        <v>1.660346467749013</v>
+      </c>
+      <c r="C154" s="14" t="n">
+        <v>2.202552830188679</v>
+      </c>
+      <c r="D154" s="14" t="n">
+        <v>2.063067134708205</v>
+      </c>
+      <c r="E154" s="14" t="n">
+        <v>5.925966432645898</v>
+      </c>
+    </row>
+    <row r="155" ht="20" customHeight="1">
+      <c r="A155" s="19" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B133" t="n">
-        <v>4.036807584269662</v>
-      </c>
-      <c r="C133" t="n">
-        <v>4.44110393258427</v>
-      </c>
-      <c r="D133" t="n">
-        <v>2.985508426966292</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="B155" s="14" t="n">
+        <v>6.725707692307693</v>
+      </c>
+      <c r="C155" s="14" t="n">
+        <v>6.781027644230768</v>
+      </c>
+      <c r="D155" s="14" t="n">
+        <v>6.921287740384616</v>
+      </c>
+      <c r="E155" s="14" t="n">
+        <v>20.42802307692308</v>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="19" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B134" t="n">
-        <v>3.50797794117647</v>
-      </c>
-      <c r="C134" t="n">
-        <v>4.676360294117647</v>
-      </c>
-      <c r="D134" t="n">
-        <v>3.43797794117647</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="B156" s="14" t="n">
+        <v>4.140147386461011</v>
+      </c>
+      <c r="C156" s="14" t="n">
+        <v>4.428366238217652</v>
+      </c>
+      <c r="D156" s="14" t="n">
+        <v>5.022782862039417</v>
+      </c>
+      <c r="E156" s="14" t="n">
+        <v>13.59129648671808</v>
+      </c>
+    </row>
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="19" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B135" t="n">
-        <v>3.551441860465117</v>
-      </c>
-      <c r="C135" t="n">
-        <v>4.348046511627906</v>
-      </c>
-      <c r="D135" t="n">
-        <v>2.394418604651163</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="B157" s="14" t="n">
+        <v>2.46666940874036</v>
+      </c>
+      <c r="C157" s="14" t="n">
+        <v>2.800198457583547</v>
+      </c>
+      <c r="D157" s="14" t="n">
+        <v>3.334798457583548</v>
+      </c>
+      <c r="E157" s="14" t="n">
+        <v>8.601666323907455</v>
+      </c>
+    </row>
+    <row r="158" ht="20" customHeight="1">
+      <c r="A158" s="19" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B136" t="n">
-        <v>3.501808988764045</v>
-      </c>
-      <c r="C136" t="n">
-        <v>4.310401685393258</v>
-      </c>
-      <c r="D136" t="n">
-        <v>3.06221488764045</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="B158" s="14" t="n">
+        <v>3.304471324762437</v>
+      </c>
+      <c r="C158" s="14" t="n">
+        <v>3.379942761319173</v>
+      </c>
+      <c r="D158" s="14" t="n">
+        <v>4.026742761319174</v>
+      </c>
+      <c r="E158" s="14" t="n">
+        <v>10.71115684740078</v>
+      </c>
+    </row>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="19" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B137" t="n">
-        <v>3.930744027303754</v>
-      </c>
-      <c r="C137" t="n">
-        <v>3.924264505119454</v>
-      </c>
-      <c r="D137" t="n">
-        <v>3.979167235494881</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="B159" s="14" t="n">
+        <v>4.956706987143655</v>
+      </c>
+      <c r="C159" s="14" t="n">
+        <v>5.035424930128563</v>
+      </c>
+      <c r="D159" s="14" t="n">
+        <v>5.999024930128565</v>
+      </c>
+      <c r="E159" s="14" t="n">
+        <v>15.99115684740078</v>
+      </c>
+    </row>
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="19" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B138" t="n">
-        <v>3.4446919127086</v>
-      </c>
-      <c r="C138" t="n">
-        <v>4.081679075738125</v>
-      </c>
-      <c r="D138" t="n">
-        <v>3.395343388960205</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="B160" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C160" s="14" t="n">
+        <v>0.5719121544537078</v>
+      </c>
+      <c r="D160" s="14" t="n">
+        <v>0.6808121544537078</v>
+      </c>
+      <c r="E160" s="14" t="n">
+        <v>1.252724308907416</v>
+      </c>
+    </row>
+    <row r="161" ht="20" customHeight="1">
+      <c r="A161" s="19" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B139" t="n">
-        <v>2.555808724832215</v>
-      </c>
-      <c r="C139" t="n">
-        <v>4.100104026845637</v>
-      </c>
-      <c r="D139" t="n">
-        <v>4.119087248322147</v>
-      </c>
-    </row>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142">
-      <c r="A142" s="13" t="inlineStr">
-        <is>
-          <t>Таблица 8. Итоговый коллективный рейтинг FR (сортировка по убыванию)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="13" t="inlineStr">
+      <c r="B161" s="14" t="n">
+        <v>4.136031533847472</v>
+      </c>
+      <c r="C161" s="14" t="n">
+        <v>4.484717395029991</v>
+      </c>
+      <c r="D161" s="14" t="n">
+        <v>5.340917395029991</v>
+      </c>
+      <c r="E161" s="14" t="n">
+        <v>13.96166632390745</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A89:D89"/>
+    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="A83:D83"/>
+    <mergeCell ref="A135:D135"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A95:D95"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A107:D107"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A149:E149"/>
+    <mergeCell ref="A44:D44"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Четкий MoSCoW_итоги</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>1) Итоговый коллективный рейтинг FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1"/>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="B143" s="13" t="inlineStr">
-        <is>
-          <t>Group_score</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Коллективный рейтинг</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B144" t="n">
-        <v>12.65945379146919</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="B6" s="14" t="n">
+        <v>22.27089552238806</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>20.42802307692308</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>15.99115684740078</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>14.0216664326459</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>13.96166632390745</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>13.59129648671808</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>10.71115684740078</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>8.601666323907455</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B145" t="n">
-        <v>12.31391139240506</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="B14" s="14" t="n">
+        <v>5.925966432645898</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>1.252724308907416</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>2) Итоговая приоритизация после учета взаимосвязанности</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Исходный рейтинг</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Скорректированный
+рейтинг</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>22.27089552238806</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>22.27089552238806</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>20.42802307692308</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>22.27089552238806</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B146" t="n">
-        <v>11.83417576791809</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="C21" s="14" t="n">
+        <v>15.99115684740078</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>15.99115684740078</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>13.96166632390745</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>15.99115684740078</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>1.252724308907416</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>15.99115684740078</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>14.0216664326459</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>14.0216664326459</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B147" t="n">
-        <v>11.62231617647059</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>FR4</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>11.46341994382023</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>FR9</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>10.92171437740693</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="C25" s="14" t="n">
+        <v>13.59129648671808</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>13.59129648671808</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B150" t="n">
-        <v>10.87442556179775</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>FR10</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>10.775</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="C26" s="14" t="n">
+        <v>10.71115684740078</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>10.71115684740078</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B152" t="n">
-        <v>10.29390697674419</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>FR2</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>6.802563829787234</v>
+      <c r="C27" s="14" t="n">
+        <v>8.601666323907455</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>10.71115684740078</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>5.925966432645898</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>5.925966432645898</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A142:F142"/>
-    <mergeCell ref="A128:F128"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A100:F100"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A114:F114"/>
-    <mergeCell ref="A86:F86"/>
+  <mergeCells count="2">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Chen 1998.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Chen 1998.xlsx
@@ -166,15 +166,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -189,6 +186,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -201,7 +201,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,6 +209,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -565,7 +568,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="11.42578125" customWidth="1" min="2" max="2"/>
     <col width="12.140625" customWidth="1" min="3" max="3"/>
     <col width="11.7109375" customWidth="1" min="4" max="4"/>
@@ -580,7 +583,7 @@
     </row>
     <row r="2"/>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Нефункциональное требование (англ. Non-functional requirements, NFR)</t>
         </is>
@@ -602,22 +605,22 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Приоритет нефункционального требования</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -658,220 +661,220 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -896,7 +899,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="30.5703125" customWidth="1" min="1" max="1"/>
     <col width="11.42578125" customWidth="1" min="2" max="2"/>
     <col width="12.140625" customWidth="1" min="3" max="3"/>
     <col width="11.7109375" customWidth="1" min="4" max="4"/>
@@ -911,7 +914,7 @@
     </row>
     <row r="2"/>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Нефункциональное требование (англ. Non-functional requirements, NFR)</t>
         </is>
@@ -933,22 +936,22 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Приоритет нефункционального требования</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -989,220 +992,220 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -1227,7 +1230,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="30.28515625" customWidth="1" min="1" max="1"/>
     <col width="11.42578125" customWidth="1" min="2" max="2"/>
     <col width="12.140625" customWidth="1" min="3" max="3"/>
     <col width="11.7109375" customWidth="1" min="4" max="4"/>
@@ -1242,7 +1245,7 @@
     </row>
     <row r="2"/>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Нефункциональное требование (англ. Non-functional requirements, NFR)</t>
         </is>
@@ -1264,22 +1267,22 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Приоритет нефункционального требования</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -1320,220 +1323,220 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -1558,7 +1561,7 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -2020,7 +2023,7 @@
   <dimension ref="A1:E161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
@@ -2030,7 +2033,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Четкий MoSCoW_расчеты</t>
+          <t>Четкий MoSCoW - расчеты (коллективная оценка, аналог Chen 1998)</t>
         </is>
       </c>
     </row>
@@ -2065,10 +2068,10 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="17" t="n">
         <v>0.75</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="17" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -2078,10 +2081,10 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="17" t="n">
         <v>0.75</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="17" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -2091,23 +2094,23 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="14" t="n">
+      <c r="B7" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="17" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>SUM</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="19" t="n">
         <v>2.5</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2143,10 +2146,10 @@
           <t>m = max(PFR) по всем экспертам и FR</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
+      <c r="B12" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="C12" s="19" t="inlineStr"/>
+      <c r="C12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
@@ -2154,10 +2157,10 @@
           <t>y1</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="17" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2167,10 +2170,10 @@
           <t>y2</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="17" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -2178,7 +2181,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>3) Индивидуальные оценки PFR_raw по экспертам</t>
+          <t>3) Ненормализованные оценки PFR_raw по экспертам</t>
         </is>
       </c>
     </row>
@@ -2206,162 +2209,162 @@
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="17" t="n">
         <v>21.5</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="17" t="n">
         <v>21.5</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
+      <c r="B20" s="17" t="n">
         <v>13.28</v>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C20" s="17" t="n">
         <v>13.5</v>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="17" t="n">
         <v>15.095</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n">
+      <c r="B21" s="17" t="n">
         <v>5.28</v>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="17" t="n">
         <v>7.095000000000001</v>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="17" t="n">
         <v>5.5</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
+      <c r="B22" s="17" t="n">
         <v>21.28</v>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="17" t="n">
         <v>21.5</v>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="17" t="n">
         <v>18.78</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B23" s="14" t="n">
+      <c r="B23" s="17" t="n">
         <v>13.2</v>
       </c>
-      <c r="C23" s="14" t="n">
+      <c r="C23" s="17" t="n">
         <v>14.19</v>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="17" t="n">
         <v>13.42</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
+      <c r="B24" s="17" t="n">
         <v>7.92</v>
       </c>
-      <c r="C24" s="14" t="n">
+      <c r="C24" s="17" t="n">
         <v>8.91</v>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="D24" s="17" t="n">
         <v>8.91</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n">
+      <c r="B25" s="17" t="n">
         <v>10.56</v>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C25" s="17" t="n">
         <v>10.78</v>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="17" t="n">
         <v>10.78</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
+      <c r="B26" s="17" t="n">
         <v>15.84</v>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="17" t="n">
         <v>16.06</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D26" s="17" t="n">
         <v>16.06</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="14" t="n">
+      <c r="B27" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="17" t="n">
         <v>1.815</v>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="17" t="n">
         <v>1.815</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="17" t="n">
         <v>13.28</v>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="17" t="n">
         <v>14.27</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="17" t="n">
         <v>14.27</v>
       </c>
     </row>
@@ -2397,162 +2400,162 @@
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="14" t="n">
+      <c r="B33" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="17" t="n">
         <v>0.8958333333333334</v>
       </c>
-      <c r="D33" s="14" t="n">
+      <c r="D33" s="17" t="n">
         <v>0.8958333333333334</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n">
+      <c r="B34" s="17" t="n">
         <v>0.5533333333333333</v>
       </c>
-      <c r="C34" s="14" t="n">
+      <c r="C34" s="17" t="n">
         <v>0.5625</v>
       </c>
-      <c r="D34" s="14" t="n">
+      <c r="D34" s="17" t="n">
         <v>0.6289583333333334</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B35" s="14" t="n">
+      <c r="B35" s="17" t="n">
         <v>0.22</v>
       </c>
-      <c r="C35" s="14" t="n">
+      <c r="C35" s="17" t="n">
         <v>0.295625</v>
       </c>
-      <c r="D35" s="14" t="n">
+      <c r="D35" s="17" t="n">
         <v>0.2291666666666667</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n">
+      <c r="B36" s="17" t="n">
         <v>0.8866666666666667</v>
       </c>
-      <c r="C36" s="14" t="n">
+      <c r="C36" s="17" t="n">
         <v>0.8958333333333334</v>
       </c>
-      <c r="D36" s="14" t="n">
+      <c r="D36" s="17" t="n">
         <v>0.7825000000000001</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B37" s="14" t="n">
+      <c r="B37" s="17" t="n">
         <v>0.55</v>
       </c>
-      <c r="C37" s="14" t="n">
+      <c r="C37" s="17" t="n">
         <v>0.5912500000000001</v>
       </c>
-      <c r="D37" s="14" t="n">
+      <c r="D37" s="17" t="n">
         <v>0.5591666666666667</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="19" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
+      <c r="B38" s="17" t="n">
         <v>0.33</v>
       </c>
-      <c r="C38" s="14" t="n">
+      <c r="C38" s="17" t="n">
         <v>0.37125</v>
       </c>
-      <c r="D38" s="14" t="n">
+      <c r="D38" s="17" t="n">
         <v>0.37125</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B39" s="14" t="n">
+      <c r="B39" s="17" t="n">
         <v>0.44</v>
       </c>
-      <c r="C39" s="14" t="n">
+      <c r="C39" s="17" t="n">
         <v>0.4491666666666667</v>
       </c>
-      <c r="D39" s="14" t="n">
+      <c r="D39" s="17" t="n">
         <v>0.4491666666666667</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B40" s="14" t="n">
+      <c r="B40" s="17" t="n">
         <v>0.66</v>
       </c>
-      <c r="C40" s="14" t="n">
+      <c r="C40" s="17" t="n">
         <v>0.6691666666666668</v>
       </c>
-      <c r="D40" s="14" t="n">
+      <c r="D40" s="17" t="n">
         <v>0.6691666666666668</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="14" t="n">
+      <c r="B41" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="17" t="n">
         <v>0.07562500000000001</v>
       </c>
-      <c r="D41" s="14" t="n">
+      <c r="D41" s="17" t="n">
         <v>0.07562500000000001</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="19" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
+      <c r="B42" s="17" t="n">
         <v>0.5533333333333333</v>
       </c>
-      <c r="C42" s="14" t="n">
+      <c r="C42" s="17" t="n">
         <v>0.5945833333333334</v>
       </c>
-      <c r="D42" s="14" t="n">
+      <c r="D42" s="17" t="n">
         <v>0.5945833333333334</v>
       </c>
     </row>
@@ -2573,7 +2576,7 @@
     </row>
     <row r="46" ht="20" customHeight="1"/>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="17" t="inlineStr">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
@@ -2603,13 +2606,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B49" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="14" t="n">
+      <c r="B49" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="17" t="n">
         <v>0.8958333333333334</v>
       </c>
-      <c r="D49" s="14" t="n">
+      <c r="D49" s="17" t="n">
         <v>0.8958333333333334</v>
       </c>
     </row>
@@ -2619,13 +2622,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B50" s="14" t="n">
+      <c r="B50" s="17" t="n">
         <v>0.8958333333333334</v>
       </c>
-      <c r="C50" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="14" t="n">
+      <c r="C50" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2635,19 +2638,19 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B51" s="14" t="n">
+      <c r="B51" s="17" t="n">
         <v>0.8958333333333334</v>
       </c>
-      <c r="C51" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="14" t="n">
+      <c r="C51" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1"/>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
@@ -2677,13 +2680,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B55" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" s="14" t="n">
+      <c r="B55" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="17" t="n">
         <v>0.9908333333333333</v>
       </c>
-      <c r="D55" s="14" t="n">
+      <c r="D55" s="17" t="n">
         <v>0.9243749999999999</v>
       </c>
     </row>
@@ -2693,13 +2696,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B56" s="14" t="n">
+      <c r="B56" s="17" t="n">
         <v>0.9908333333333333</v>
       </c>
-      <c r="C56" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="14" t="n">
+      <c r="C56" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="17" t="n">
         <v>0.9335416666666666</v>
       </c>
     </row>
@@ -2709,19 +2712,19 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B57" s="14" t="n">
+      <c r="B57" s="17" t="n">
         <v>0.9243749999999999</v>
       </c>
-      <c r="C57" s="14" t="n">
+      <c r="C57" s="17" t="n">
         <v>0.9335416666666666</v>
       </c>
-      <c r="D57" s="14" t="n">
+      <c r="D57" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1"/>
     <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="17" t="inlineStr">
+      <c r="A59" s="18" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
@@ -2751,13 +2754,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B61" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="14" t="n">
+      <c r="B61" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="17" t="n">
         <v>0.9243749999999999</v>
       </c>
-      <c r="D61" s="14" t="n">
+      <c r="D61" s="17" t="n">
         <v>0.9908333333333333</v>
       </c>
     </row>
@@ -2767,13 +2770,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B62" s="14" t="n">
+      <c r="B62" s="17" t="n">
         <v>0.9243749999999999</v>
       </c>
-      <c r="C62" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="14" t="n">
+      <c r="C62" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="17" t="n">
         <v>0.9335416666666666</v>
       </c>
     </row>
@@ -2783,19 +2786,19 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B63" s="14" t="n">
+      <c r="B63" s="17" t="n">
         <v>0.9908333333333333</v>
       </c>
-      <c r="C63" s="14" t="n">
+      <c r="C63" s="17" t="n">
         <v>0.9335416666666666</v>
       </c>
-      <c r="D63" s="14" t="n">
+      <c r="D63" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1"/>
     <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="17" t="inlineStr">
+      <c r="A65" s="18" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
@@ -2825,13 +2828,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B67" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" s="14" t="n">
+      <c r="B67" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="17" t="n">
         <v>0.9908333333333333</v>
       </c>
-      <c r="D67" s="14" t="n">
+      <c r="D67" s="17" t="n">
         <v>0.8958333333333334</v>
       </c>
     </row>
@@ -2841,13 +2844,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B68" s="14" t="n">
+      <c r="B68" s="17" t="n">
         <v>0.9908333333333333</v>
       </c>
-      <c r="C68" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" s="14" t="n">
+      <c r="C68" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="17" t="n">
         <v>0.8866666666666667</v>
       </c>
     </row>
@@ -2857,19 +2860,19 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B69" s="14" t="n">
+      <c r="B69" s="17" t="n">
         <v>0.8958333333333334</v>
       </c>
-      <c r="C69" s="14" t="n">
+      <c r="C69" s="17" t="n">
         <v>0.8866666666666667</v>
       </c>
-      <c r="D69" s="14" t="n">
+      <c r="D69" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1"/>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="17" t="inlineStr">
+      <c r="A71" s="18" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
@@ -2899,13 +2902,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B73" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C73" s="14" t="n">
+      <c r="B73" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" s="17" t="n">
         <v>0.95875</v>
       </c>
-      <c r="D73" s="14" t="n">
+      <c r="D73" s="17" t="n">
         <v>0.9908333333333333</v>
       </c>
     </row>
@@ -2915,13 +2918,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B74" s="14" t="n">
+      <c r="B74" s="17" t="n">
         <v>0.95875</v>
       </c>
-      <c r="C74" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" s="14" t="n">
+      <c r="C74" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="17" t="n">
         <v>0.9679166666666666</v>
       </c>
     </row>
@@ -2931,19 +2934,19 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B75" s="14" t="n">
+      <c r="B75" s="17" t="n">
         <v>0.9908333333333333</v>
       </c>
-      <c r="C75" s="14" t="n">
+      <c r="C75" s="17" t="n">
         <v>0.9679166666666666</v>
       </c>
-      <c r="D75" s="14" t="n">
+      <c r="D75" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1"/>
     <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="17" t="inlineStr">
+      <c r="A77" s="18" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
@@ -2973,13 +2976,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B79" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C79" s="14" t="n">
+      <c r="B79" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="17" t="n">
         <v>0.95875</v>
       </c>
-      <c r="D79" s="14" t="n">
+      <c r="D79" s="17" t="n">
         <v>0.95875</v>
       </c>
     </row>
@@ -2989,13 +2992,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B80" s="14" t="n">
+      <c r="B80" s="17" t="n">
         <v>0.95875</v>
       </c>
-      <c r="C80" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" s="14" t="n">
+      <c r="C80" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3005,19 +3008,19 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B81" s="14" t="n">
+      <c r="B81" s="17" t="n">
         <v>0.95875</v>
       </c>
-      <c r="C81" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" s="14" t="n">
+      <c r="C81" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1"/>
     <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="17" t="inlineStr">
+      <c r="A83" s="18" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
@@ -3047,13 +3050,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B85" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" s="14" t="n">
+      <c r="B85" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="17" t="n">
         <v>0.9908333333333332</v>
       </c>
-      <c r="D85" s="14" t="n">
+      <c r="D85" s="17" t="n">
         <v>0.9908333333333332</v>
       </c>
     </row>
@@ -3063,13 +3066,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B86" s="14" t="n">
+      <c r="B86" s="17" t="n">
         <v>0.9908333333333332</v>
       </c>
-      <c r="C86" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" s="14" t="n">
+      <c r="C86" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3079,19 +3082,19 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B87" s="14" t="n">
+      <c r="B87" s="17" t="n">
         <v>0.9908333333333332</v>
       </c>
-      <c r="C87" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" s="14" t="n">
+      <c r="C87" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1"/>
     <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="17" t="inlineStr">
+      <c r="A89" s="18" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
@@ -3121,13 +3124,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B91" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C91" s="14" t="n">
+      <c r="B91" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" s="17" t="n">
         <v>0.9908333333333332</v>
       </c>
-      <c r="D91" s="14" t="n">
+      <c r="D91" s="17" t="n">
         <v>0.9908333333333332</v>
       </c>
     </row>
@@ -3137,13 +3140,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B92" s="14" t="n">
+      <c r="B92" s="17" t="n">
         <v>0.9908333333333332</v>
       </c>
-      <c r="C92" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" s="14" t="n">
+      <c r="C92" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3153,19 +3156,19 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B93" s="14" t="n">
+      <c r="B93" s="17" t="n">
         <v>0.9908333333333332</v>
       </c>
-      <c r="C93" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D93" s="14" t="n">
+      <c r="C93" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1"/>
     <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="17" t="inlineStr">
+      <c r="A95" s="18" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
@@ -3195,13 +3198,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B97" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C97" s="14" t="n">
+      <c r="B97" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" s="17" t="n">
         <v>0.9243749999999999</v>
       </c>
-      <c r="D97" s="14" t="n">
+      <c r="D97" s="17" t="n">
         <v>0.9243749999999999</v>
       </c>
     </row>
@@ -3211,13 +3214,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B98" s="14" t="n">
+      <c r="B98" s="17" t="n">
         <v>0.9243749999999999</v>
       </c>
-      <c r="C98" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" s="14" t="n">
+      <c r="C98" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3227,19 +3230,19 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B99" s="14" t="n">
+      <c r="B99" s="17" t="n">
         <v>0.9243749999999999</v>
       </c>
-      <c r="C99" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D99" s="14" t="n">
+      <c r="C99" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1"/>
     <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="17" t="inlineStr">
+      <c r="A101" s="18" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
@@ -3269,13 +3272,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B103" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C103" s="14" t="n">
+      <c r="B103" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" s="17" t="n">
         <v>0.95875</v>
       </c>
-      <c r="D103" s="14" t="n">
+      <c r="D103" s="17" t="n">
         <v>0.95875</v>
       </c>
     </row>
@@ -3285,13 +3288,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B104" s="14" t="n">
+      <c r="B104" s="17" t="n">
         <v>0.95875</v>
       </c>
-      <c r="C104" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D104" s="14" t="n">
+      <c r="C104" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3301,13 +3304,13 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B105" s="14" t="n">
+      <c r="B105" s="17" t="n">
         <v>0.95875</v>
       </c>
-      <c r="C105" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D105" s="14" t="n">
+      <c r="C105" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3343,162 +3346,162 @@
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="19" t="inlineStr">
+      <c r="A110" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B110" s="14" t="n">
+      <c r="B110" s="17" t="n">
         <v>0.8958333333333334</v>
       </c>
-      <c r="C110" s="14" t="n">
+      <c r="C110" s="17" t="n">
         <v>0.9479166666666667</v>
       </c>
-      <c r="D110" s="14" t="n">
+      <c r="D110" s="17" t="n">
         <v>0.9479166666666667</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="19" t="inlineStr">
+      <c r="A111" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B111" s="14" t="n">
+      <c r="B111" s="17" t="n">
         <v>0.9576041666666666</v>
       </c>
-      <c r="C111" s="14" t="n">
+      <c r="C111" s="17" t="n">
         <v>0.9621875</v>
       </c>
-      <c r="D111" s="14" t="n">
+      <c r="D111" s="17" t="n">
         <v>0.9289583333333333</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="19" t="inlineStr">
+      <c r="A112" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B112" s="14" t="n">
+      <c r="B112" s="17" t="n">
         <v>0.9576041666666666</v>
       </c>
-      <c r="C112" s="14" t="n">
+      <c r="C112" s="17" t="n">
         <v>0.9289583333333333</v>
       </c>
-      <c r="D112" s="14" t="n">
+      <c r="D112" s="17" t="n">
         <v>0.9621875</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="19" t="inlineStr">
+      <c r="A113" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B113" s="14" t="n">
+      <c r="B113" s="17" t="n">
         <v>0.9433333333333334</v>
       </c>
-      <c r="C113" s="14" t="n">
+      <c r="C113" s="17" t="n">
         <v>0.93875</v>
       </c>
-      <c r="D113" s="14" t="n">
+      <c r="D113" s="17" t="n">
         <v>0.8912500000000001</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="19" t="inlineStr">
+      <c r="A114" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B114" s="14" t="n">
+      <c r="B114" s="17" t="n">
         <v>0.9747916666666667</v>
       </c>
-      <c r="C114" s="14" t="n">
+      <c r="C114" s="17" t="n">
         <v>0.9633333333333334</v>
       </c>
-      <c r="D114" s="14" t="n">
+      <c r="D114" s="17" t="n">
         <v>0.979375</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="19" t="inlineStr">
+      <c r="A115" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B115" s="14" t="n">
+      <c r="B115" s="17" t="n">
         <v>0.95875</v>
       </c>
-      <c r="C115" s="14" t="n">
+      <c r="C115" s="17" t="n">
         <v>0.979375</v>
       </c>
-      <c r="D115" s="14" t="n">
+      <c r="D115" s="17" t="n">
         <v>0.979375</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="19" t="inlineStr">
+      <c r="A116" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B116" s="14" t="n">
+      <c r="B116" s="17" t="n">
         <v>0.9908333333333332</v>
       </c>
-      <c r="C116" s="14" t="n">
+      <c r="C116" s="17" t="n">
         <v>0.9954166666666666</v>
       </c>
-      <c r="D116" s="14" t="n">
+      <c r="D116" s="17" t="n">
         <v>0.9954166666666666</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="19" t="inlineStr">
+      <c r="A117" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B117" s="14" t="n">
+      <c r="B117" s="17" t="n">
         <v>0.9908333333333332</v>
       </c>
-      <c r="C117" s="14" t="n">
+      <c r="C117" s="17" t="n">
         <v>0.9954166666666666</v>
       </c>
-      <c r="D117" s="14" t="n">
+      <c r="D117" s="17" t="n">
         <v>0.9954166666666666</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="19" t="inlineStr">
+      <c r="A118" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B118" s="14" t="n">
+      <c r="B118" s="17" t="n">
         <v>0.9243749999999999</v>
       </c>
-      <c r="C118" s="14" t="n">
+      <c r="C118" s="17" t="n">
         <v>0.9621875</v>
       </c>
-      <c r="D118" s="14" t="n">
+      <c r="D118" s="17" t="n">
         <v>0.9621875</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="19" t="inlineStr">
+      <c r="A119" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B119" s="14" t="n">
+      <c r="B119" s="17" t="n">
         <v>0.95875</v>
       </c>
-      <c r="C119" s="14" t="n">
+      <c r="C119" s="17" t="n">
         <v>0.979375</v>
       </c>
-      <c r="D119" s="14" t="n">
+      <c r="D119" s="17" t="n">
         <v>0.979375</v>
       </c>
     </row>
@@ -3534,162 +3537,162 @@
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="19" t="inlineStr">
+      <c r="A124" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B124" s="14" t="n">
+      <c r="B124" s="17" t="n">
         <v>0.3208955223880597</v>
       </c>
-      <c r="C124" s="14" t="n">
+      <c r="C124" s="17" t="n">
         <v>0.3395522388059701</v>
       </c>
-      <c r="D124" s="14" t="n">
+      <c r="D124" s="17" t="n">
         <v>0.3395522388059701</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="19" t="inlineStr">
+      <c r="A125" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B125" s="14" t="n">
+      <c r="B125" s="17" t="n">
         <v>0.3361488957144946</v>
       </c>
-      <c r="C125" s="14" t="n">
+      <c r="C125" s="17" t="n">
         <v>0.3377577885037297</v>
       </c>
-      <c r="D125" s="14" t="n">
+      <c r="D125" s="17" t="n">
         <v>0.3260933157817756</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="19" t="inlineStr">
+      <c r="A126" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B126" s="14" t="n">
+      <c r="B126" s="17" t="n">
         <v>0.3361488957144946</v>
       </c>
-      <c r="C126" s="14" t="n">
+      <c r="C126" s="17" t="n">
         <v>0.3260933157817756</v>
       </c>
-      <c r="D126" s="14" t="n">
+      <c r="D126" s="17" t="n">
         <v>0.3377577885037297</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="19" t="inlineStr">
+      <c r="A127" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B127" s="14" t="n">
+      <c r="B127" s="17" t="n">
         <v>0.3401442307692308</v>
       </c>
-      <c r="C127" s="14" t="n">
+      <c r="C127" s="17" t="n">
         <v>0.3384915865384615</v>
       </c>
-      <c r="D127" s="14" t="n">
+      <c r="D127" s="17" t="n">
         <v>0.3213641826923077</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="19" t="inlineStr">
+      <c r="A128" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B128" s="14" t="n">
+      <c r="B128" s="17" t="n">
         <v>0.3341188231933733</v>
       </c>
-      <c r="C128" s="14" t="n">
+      <c r="C128" s="17" t="n">
         <v>0.3301913738931734</v>
       </c>
-      <c r="D128" s="14" t="n">
+      <c r="D128" s="17" t="n">
         <v>0.3356898029134533</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="19" t="inlineStr">
+      <c r="A129" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B129" s="14" t="n">
+      <c r="B129" s="17" t="n">
         <v>0.3286203941730934</v>
       </c>
-      <c r="C129" s="14" t="n">
+      <c r="C129" s="17" t="n">
         <v>0.3356898029134533</v>
       </c>
-      <c r="D129" s="14" t="n">
+      <c r="D129" s="17" t="n">
         <v>0.3356898029134533</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="19" t="inlineStr">
+      <c r="A130" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B130" s="14" t="n">
+      <c r="B130" s="17" t="n">
         <v>0.3323085522638345</v>
       </c>
-      <c r="C130" s="14" t="n">
+      <c r="C130" s="17" t="n">
         <v>0.3338457238680828</v>
       </c>
-      <c r="D130" s="14" t="n">
+      <c r="D130" s="17" t="n">
         <v>0.3338457238680828</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="19" t="inlineStr">
+      <c r="A131" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B131" s="14" t="n">
+      <c r="B131" s="17" t="n">
         <v>0.3323085522638345</v>
       </c>
-      <c r="C131" s="14" t="n">
+      <c r="C131" s="17" t="n">
         <v>0.3338457238680828</v>
       </c>
-      <c r="D131" s="14" t="n">
+      <c r="D131" s="17" t="n">
         <v>0.3338457238680828</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="19" t="inlineStr">
+      <c r="A132" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B132" s="14" t="n">
+      <c r="B132" s="17" t="n">
         <v>0.3244844229925406</v>
       </c>
-      <c r="C132" s="14" t="n">
+      <c r="C132" s="17" t="n">
         <v>0.3377577885037297</v>
       </c>
-      <c r="D132" s="14" t="n">
+      <c r="D132" s="17" t="n">
         <v>0.3377577885037297</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="19" t="inlineStr">
+      <c r="A133" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B133" s="14" t="n">
+      <c r="B133" s="17" t="n">
         <v>0.3286203941730934</v>
       </c>
-      <c r="C133" s="14" t="n">
+      <c r="C133" s="17" t="n">
         <v>0.3356898029134533</v>
       </c>
-      <c r="D133" s="14" t="n">
+      <c r="D133" s="17" t="n">
         <v>0.3356898029134533</v>
       </c>
     </row>
@@ -3725,162 +3728,162 @@
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="19" t="inlineStr">
+      <c r="A138" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B138" s="14" t="n">
+      <c r="B138" s="17" t="n">
         <v>0.3083582089552239</v>
       </c>
-      <c r="C138" s="14" t="n">
+      <c r="C138" s="17" t="n">
         <v>0.315820895522388</v>
       </c>
-      <c r="D138" s="14" t="n">
+      <c r="D138" s="17" t="n">
         <v>0.3758208955223881</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="19" t="inlineStr">
+      <c r="A139" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B139" s="14" t="n">
+      <c r="B139" s="17" t="n">
         <v>0.3144595582857979</v>
       </c>
-      <c r="C139" s="14" t="n">
+      <c r="C139" s="17" t="n">
         <v>0.3151031154014919</v>
       </c>
-      <c r="D139" s="14" t="n">
+      <c r="D139" s="17" t="n">
         <v>0.3704373263127102</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="19" t="inlineStr">
+      <c r="A140" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B140" s="14" t="n">
+      <c r="B140" s="17" t="n">
         <v>0.3144595582857979</v>
       </c>
-      <c r="C140" s="14" t="n">
+      <c r="C140" s="17" t="n">
         <v>0.3104373263127103</v>
       </c>
-      <c r="D140" s="14" t="n">
+      <c r="D140" s="17" t="n">
         <v>0.3751031154014919</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="19" t="inlineStr">
+      <c r="A141" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B141" s="14" t="n">
+      <c r="B141" s="17" t="n">
         <v>0.3160576923076923</v>
       </c>
-      <c r="C141" s="14" t="n">
+      <c r="C141" s="17" t="n">
         <v>0.3153966346153846</v>
       </c>
-      <c r="D141" s="14" t="n">
+      <c r="D141" s="17" t="n">
         <v>0.3685456730769231</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="19" t="inlineStr">
+      <c r="A142" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B142" s="14" t="n">
+      <c r="B142" s="17" t="n">
         <v>0.3136475292773493</v>
       </c>
-      <c r="C142" s="14" t="n">
+      <c r="C142" s="17" t="n">
         <v>0.3120765495572693</v>
       </c>
-      <c r="D142" s="14" t="n">
+      <c r="D142" s="17" t="n">
         <v>0.3742759211653813</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="19" t="inlineStr">
+      <c r="A143" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B143" s="14" t="n">
+      <c r="B143" s="17" t="n">
         <v>0.3114481576692373</v>
       </c>
-      <c r="C143" s="14" t="n">
+      <c r="C143" s="17" t="n">
         <v>0.3142759211653813</v>
       </c>
-      <c r="D143" s="14" t="n">
+      <c r="D143" s="17" t="n">
         <v>0.3742759211653813</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
-      <c r="A144" s="19" t="inlineStr">
+      <c r="A144" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B144" s="14" t="n">
+      <c r="B144" s="17" t="n">
         <v>0.3129234209055338</v>
       </c>
-      <c r="C144" s="14" t="n">
+      <c r="C144" s="17" t="n">
         <v>0.3135382895472331</v>
       </c>
-      <c r="D144" s="14" t="n">
+      <c r="D144" s="17" t="n">
         <v>0.3735382895472331</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="19" t="inlineStr">
+      <c r="A145" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B145" s="14" t="n">
+      <c r="B145" s="17" t="n">
         <v>0.3129234209055338</v>
       </c>
-      <c r="C145" s="14" t="n">
+      <c r="C145" s="17" t="n">
         <v>0.3135382895472331</v>
       </c>
-      <c r="D145" s="14" t="n">
+      <c r="D145" s="17" t="n">
         <v>0.3735382895472331</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="19" t="inlineStr">
+      <c r="A146" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B146" s="14" t="n">
+      <c r="B146" s="17" t="n">
         <v>0.3097937691970162</v>
       </c>
-      <c r="C146" s="14" t="n">
+      <c r="C146" s="17" t="n">
         <v>0.3151031154014919</v>
       </c>
-      <c r="D146" s="14" t="n">
+      <c r="D146" s="17" t="n">
         <v>0.3751031154014919</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
-      <c r="A147" s="19" t="inlineStr">
+      <c r="A147" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B147" s="14" t="n">
+      <c r="B147" s="17" t="n">
         <v>0.3114481576692373</v>
       </c>
-      <c r="C147" s="14" t="n">
+      <c r="C147" s="17" t="n">
         <v>0.3142759211653813</v>
       </c>
-      <c r="D147" s="14" t="n">
+      <c r="D147" s="17" t="n">
         <v>0.3742759211653813</v>
       </c>
     </row>
@@ -3921,192 +3924,192 @@
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
-      <c r="A152" s="19" t="inlineStr">
+      <c r="A152" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B152" s="14" t="n">
+      <c r="B152" s="17" t="n">
         <v>7.400597014925372</v>
       </c>
-      <c r="C152" s="14" t="n">
+      <c r="C152" s="17" t="n">
         <v>6.790149253731342</v>
       </c>
-      <c r="D152" s="14" t="n">
+      <c r="D152" s="17" t="n">
         <v>8.080149253731344</v>
       </c>
-      <c r="E152" s="14" t="n">
+      <c r="E152" s="17" t="n">
         <v>22.27089552238806</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
-      <c r="A153" s="19" t="inlineStr">
+      <c r="A153" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B153" s="14" t="n">
+      <c r="B153" s="17" t="n">
         <v>4.176022934035396</v>
       </c>
-      <c r="C153" s="14" t="n">
+      <c r="C153" s="17" t="n">
         <v>4.25389205792014</v>
       </c>
-      <c r="D153" s="14" t="n">
+      <c r="D153" s="17" t="n">
         <v>5.591751440690361</v>
       </c>
-      <c r="E153" s="14" t="n">
+      <c r="E153" s="17" t="n">
         <v>14.0216664326459</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
-      <c r="A154" s="19" t="inlineStr">
+      <c r="A154" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B154" s="14" t="n">
+      <c r="B154" s="17" t="n">
         <v>1.660346467749013</v>
       </c>
-      <c r="C154" s="14" t="n">
+      <c r="C154" s="17" t="n">
         <v>2.202552830188679</v>
       </c>
-      <c r="D154" s="14" t="n">
+      <c r="D154" s="17" t="n">
         <v>2.063067134708205</v>
       </c>
-      <c r="E154" s="14" t="n">
+      <c r="E154" s="17" t="n">
         <v>5.925966432645898</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
-      <c r="A155" s="19" t="inlineStr">
+      <c r="A155" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B155" s="14" t="n">
+      <c r="B155" s="17" t="n">
         <v>6.725707692307693</v>
       </c>
-      <c r="C155" s="14" t="n">
+      <c r="C155" s="17" t="n">
         <v>6.781027644230768</v>
       </c>
-      <c r="D155" s="14" t="n">
+      <c r="D155" s="17" t="n">
         <v>6.921287740384616</v>
       </c>
-      <c r="E155" s="14" t="n">
+      <c r="E155" s="17" t="n">
         <v>20.42802307692308</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
-      <c r="A156" s="19" t="inlineStr">
+      <c r="A156" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B156" s="14" t="n">
+      <c r="B156" s="17" t="n">
         <v>4.140147386461011</v>
       </c>
-      <c r="C156" s="14" t="n">
+      <c r="C156" s="17" t="n">
         <v>4.428366238217652</v>
       </c>
-      <c r="D156" s="14" t="n">
+      <c r="D156" s="17" t="n">
         <v>5.022782862039417</v>
       </c>
-      <c r="E156" s="14" t="n">
+      <c r="E156" s="17" t="n">
         <v>13.59129648671808</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
-      <c r="A157" s="19" t="inlineStr">
+      <c r="A157" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B157" s="14" t="n">
+      <c r="B157" s="17" t="n">
         <v>2.46666940874036</v>
       </c>
-      <c r="C157" s="14" t="n">
+      <c r="C157" s="17" t="n">
         <v>2.800198457583547</v>
       </c>
-      <c r="D157" s="14" t="n">
+      <c r="D157" s="17" t="n">
         <v>3.334798457583548</v>
       </c>
-      <c r="E157" s="14" t="n">
+      <c r="E157" s="17" t="n">
         <v>8.601666323907455</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
-      <c r="A158" s="19" t="inlineStr">
+      <c r="A158" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B158" s="14" t="n">
+      <c r="B158" s="17" t="n">
         <v>3.304471324762437</v>
       </c>
-      <c r="C158" s="14" t="n">
+      <c r="C158" s="17" t="n">
         <v>3.379942761319173</v>
       </c>
-      <c r="D158" s="14" t="n">
+      <c r="D158" s="17" t="n">
         <v>4.026742761319174</v>
       </c>
-      <c r="E158" s="14" t="n">
+      <c r="E158" s="17" t="n">
         <v>10.71115684740078</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
-      <c r="A159" s="19" t="inlineStr">
+      <c r="A159" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B159" s="14" t="n">
+      <c r="B159" s="17" t="n">
         <v>4.956706987143655</v>
       </c>
-      <c r="C159" s="14" t="n">
+      <c r="C159" s="17" t="n">
         <v>5.035424930128563</v>
       </c>
-      <c r="D159" s="14" t="n">
+      <c r="D159" s="17" t="n">
         <v>5.999024930128565</v>
       </c>
-      <c r="E159" s="14" t="n">
+      <c r="E159" s="17" t="n">
         <v>15.99115684740078</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
-      <c r="A160" s="19" t="inlineStr">
+      <c r="A160" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B160" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C160" s="14" t="n">
+      <c r="B160" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C160" s="17" t="n">
         <v>0.5719121544537078</v>
       </c>
-      <c r="D160" s="14" t="n">
+      <c r="D160" s="17" t="n">
         <v>0.6808121544537078</v>
       </c>
-      <c r="E160" s="14" t="n">
+      <c r="E160" s="17" t="n">
         <v>1.252724308907416</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
-      <c r="A161" s="19" t="inlineStr">
+      <c r="A161" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B161" s="14" t="n">
+      <c r="B161" s="17" t="n">
         <v>4.136031533847472</v>
       </c>
-      <c r="C161" s="14" t="n">
+      <c r="C161" s="17" t="n">
         <v>4.484717395029991</v>
       </c>
-      <c r="D161" s="14" t="n">
+      <c r="D161" s="17" t="n">
         <v>5.340917395029991</v>
       </c>
-      <c r="E161" s="14" t="n">
+      <c r="E161" s="17" t="n">
         <v>13.96166632390745</v>
       </c>
     </row>
@@ -4144,7 +4147,7 @@
   <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -4153,7 +4156,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Четкий MoSCoW_итоги</t>
+          <t>Четкий MoSCoW - итоги (коллективная оценка, аналог Chen 1998)</t>
         </is>
       </c>
     </row>
@@ -4179,102 +4182,102 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="17" t="n">
         <v>22.27089552238806</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="17" t="n">
         <v>20.42802307692308</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="17" t="n">
         <v>15.99115684740078</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="17" t="n">
         <v>14.0216664326459</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="17" t="n">
         <v>13.96166632390745</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="17" t="n">
         <v>13.59129648671808</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
+      <c r="B12" s="17" t="n">
         <v>10.71115684740078</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="17" t="n">
         <v>8.601666323907455</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="17" t="n">
         <v>5.925966432645898</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B15" s="17" t="n">
         <v>1.252724308907416</v>
       </c>
     </row>
@@ -4313,15 +4316,15 @@
       <c r="A19" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="17" t="n">
         <v>22.27089552238806</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="17" t="n">
         <v>22.27089552238806</v>
       </c>
     </row>
@@ -4329,15 +4332,15 @@
       <c r="A20" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C20" s="17" t="n">
         <v>20.42802307692308</v>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="17" t="n">
         <v>22.27089552238806</v>
       </c>
     </row>
@@ -4345,15 +4348,15 @@
       <c r="A21" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="17" t="n">
         <v>15.99115684740078</v>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="17" t="n">
         <v>15.99115684740078</v>
       </c>
     </row>
@@ -4361,15 +4364,15 @@
       <c r="A22" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="17" t="n">
         <v>13.96166632390745</v>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="17" t="n">
         <v>15.99115684740078</v>
       </c>
     </row>
@@ -4377,15 +4380,15 @@
       <c r="A23" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C23" s="14" t="n">
+      <c r="C23" s="17" t="n">
         <v>1.252724308907416</v>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="17" t="n">
         <v>15.99115684740078</v>
       </c>
     </row>
@@ -4393,15 +4396,15 @@
       <c r="A24" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="C24" s="14" t="n">
+      <c r="C24" s="17" t="n">
         <v>14.0216664326459</v>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="D24" s="17" t="n">
         <v>14.0216664326459</v>
       </c>
     </row>
@@ -4409,15 +4412,15 @@
       <c r="A25" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C25" s="17" t="n">
         <v>13.59129648671808</v>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="17" t="n">
         <v>13.59129648671808</v>
       </c>
     </row>
@@ -4425,15 +4428,15 @@
       <c r="A26" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="17" t="n">
         <v>10.71115684740078</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D26" s="17" t="n">
         <v>10.71115684740078</v>
       </c>
     </row>
@@ -4441,15 +4444,15 @@
       <c r="A27" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="17" t="n">
         <v>8.601666323907455</v>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="17" t="n">
         <v>10.71115684740078</v>
       </c>
     </row>
@@ -4457,15 +4460,15 @@
       <c r="A28" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="17" t="n">
         <v>5.925966432645898</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="17" t="n">
         <v>5.925966432645898</v>
       </c>
     </row>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Chen 1998.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Chen 1998.xlsx
@@ -2118,7 +2118,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>2) Параметры алгоритма и нормализации</t>
+          <t>2) Гиперпараметры модели</t>
         </is>
       </c>
     </row>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Chen 1998.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Chen 1998.xlsx
@@ -2118,7 +2118,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>2) Гиперпараметры модели</t>
+          <t>2) Параметры модели</t>
         </is>
       </c>
     </row>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Chen 1998.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Chen 1998.xlsx
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C13" s="17" t="n">
         <v>0.6</v>
-      </c>
-      <c r="C13" s="17" t="n">
-        <v>0.9</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1"/>
@@ -3734,13 +3734,13 @@
         </is>
       </c>
       <c r="B138" s="17" t="n">
-        <v>0.3083582089552239</v>
+        <v>0.3125373134328358</v>
       </c>
       <c r="C138" s="17" t="n">
-        <v>0.315820895522388</v>
+        <v>0.3237313432835821</v>
       </c>
       <c r="D138" s="17" t="n">
-        <v>0.3758208955223881</v>
+        <v>0.3637313432835821</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="B139" s="17" t="n">
-        <v>0.3144595582857979</v>
+        <v>0.3216893374286968</v>
       </c>
       <c r="C139" s="17" t="n">
-        <v>0.3151031154014919</v>
+        <v>0.3226546731022378</v>
       </c>
       <c r="D139" s="17" t="n">
-        <v>0.3704373263127102</v>
+        <v>0.3556559894690654</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -3766,13 +3766,13 @@
         </is>
       </c>
       <c r="B140" s="17" t="n">
-        <v>0.3144595582857979</v>
+        <v>0.3216893374286968</v>
       </c>
       <c r="C140" s="17" t="n">
-        <v>0.3104373263127103</v>
+        <v>0.3156559894690654</v>
       </c>
       <c r="D140" s="17" t="n">
-        <v>0.3751031154014919</v>
+        <v>0.3626546731022379</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -3782,13 +3782,13 @@
         </is>
       </c>
       <c r="B141" s="17" t="n">
-        <v>0.3160576923076923</v>
+        <v>0.3240865384615385</v>
       </c>
       <c r="C141" s="17" t="n">
-        <v>0.3153966346153846</v>
+        <v>0.3230949519230769</v>
       </c>
       <c r="D141" s="17" t="n">
-        <v>0.3685456730769231</v>
+        <v>0.3528185096153846</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -3798,13 +3798,13 @@
         </is>
       </c>
       <c r="B142" s="17" t="n">
-        <v>0.3136475292773493</v>
+        <v>0.320471293916024</v>
       </c>
       <c r="C142" s="17" t="n">
-        <v>0.3120765495572693</v>
+        <v>0.318114824335904</v>
       </c>
       <c r="D142" s="17" t="n">
-        <v>0.3742759211653813</v>
+        <v>0.361413881748072</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -3814,13 +3814,13 @@
         </is>
       </c>
       <c r="B143" s="17" t="n">
-        <v>0.3114481576692373</v>
+        <v>0.317172236503856</v>
       </c>
       <c r="C143" s="17" t="n">
-        <v>0.3142759211653813</v>
+        <v>0.321413881748072</v>
       </c>
       <c r="D143" s="17" t="n">
-        <v>0.3742759211653813</v>
+        <v>0.361413881748072</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="B144" s="17" t="n">
-        <v>0.3129234209055338</v>
+        <v>0.3193851313583007</v>
       </c>
       <c r="C144" s="17" t="n">
-        <v>0.3135382895472331</v>
+        <v>0.3203074343208496</v>
       </c>
       <c r="D144" s="17" t="n">
-        <v>0.3735382895472331</v>
+        <v>0.3603074343208497</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -3846,13 +3846,13 @@
         </is>
       </c>
       <c r="B145" s="17" t="n">
-        <v>0.3129234209055338</v>
+        <v>0.3193851313583007</v>
       </c>
       <c r="C145" s="17" t="n">
-        <v>0.3135382895472331</v>
+        <v>0.3203074343208496</v>
       </c>
       <c r="D145" s="17" t="n">
-        <v>0.3735382895472331</v>
+        <v>0.3603074343208497</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="B146" s="17" t="n">
-        <v>0.3097937691970162</v>
+        <v>0.3146906537955244</v>
       </c>
       <c r="C146" s="17" t="n">
-        <v>0.3151031154014919</v>
+        <v>0.3226546731022378</v>
       </c>
       <c r="D146" s="17" t="n">
-        <v>0.3751031154014919</v>
+        <v>0.3626546731022379</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -3878,13 +3878,13 @@
         </is>
       </c>
       <c r="B147" s="17" t="n">
-        <v>0.3114481576692373</v>
+        <v>0.317172236503856</v>
       </c>
       <c r="C147" s="17" t="n">
-        <v>0.3142759211653813</v>
+        <v>0.321413881748072</v>
       </c>
       <c r="D147" s="17" t="n">
-        <v>0.3742759211653813</v>
+        <v>0.361413881748072</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1"/>
@@ -3930,16 +3930,16 @@
         </is>
       </c>
       <c r="B152" s="17" t="n">
-        <v>7.400597014925372</v>
+        <v>7.50089552238806</v>
       </c>
       <c r="C152" s="17" t="n">
-        <v>6.790149253731342</v>
+        <v>6.960223880597014</v>
       </c>
       <c r="D152" s="17" t="n">
-        <v>8.080149253731344</v>
+        <v>7.820223880597015</v>
       </c>
       <c r="E152" s="17" t="n">
-        <v>22.27089552238806</v>
+        <v>22.28134328358209</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -3949,16 +3949,16 @@
         </is>
       </c>
       <c r="B153" s="17" t="n">
-        <v>4.176022934035396</v>
+        <v>4.272034401053094</v>
       </c>
       <c r="C153" s="17" t="n">
-        <v>4.25389205792014</v>
+        <v>4.355838086880211</v>
       </c>
       <c r="D153" s="17" t="n">
-        <v>5.591751440690361</v>
+        <v>5.368627161035542</v>
       </c>
       <c r="E153" s="17" t="n">
-        <v>14.0216664326459</v>
+        <v>13.99649964896885</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -3968,16 +3968,16 @@
         </is>
       </c>
       <c r="B154" s="17" t="n">
-        <v>1.660346467749013</v>
+        <v>1.698519701623519</v>
       </c>
       <c r="C154" s="17" t="n">
-        <v>2.202552830188679</v>
+        <v>2.239579245283019</v>
       </c>
       <c r="D154" s="17" t="n">
-        <v>2.063067134708205</v>
+        <v>1.994600702062308</v>
       </c>
       <c r="E154" s="17" t="n">
-        <v>5.925966432645898</v>
+        <v>5.932699648968846</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -3987,16 +3987,16 @@
         </is>
       </c>
       <c r="B155" s="17" t="n">
-        <v>6.725707692307693</v>
+        <v>6.896561538461539</v>
       </c>
       <c r="C155" s="17" t="n">
-        <v>6.781027644230768</v>
+        <v>6.946541466346153</v>
       </c>
       <c r="D155" s="17" t="n">
-        <v>6.921287740384616</v>
+        <v>6.625931610576924</v>
       </c>
       <c r="E155" s="17" t="n">
-        <v>20.42802307692308</v>
+        <v>20.46903461538461</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4006,16 +4006,16 @@
         </is>
       </c>
       <c r="B156" s="17" t="n">
-        <v>4.140147386461011</v>
+        <v>4.230221079691517</v>
       </c>
       <c r="C156" s="17" t="n">
-        <v>4.428366238217652</v>
+        <v>4.514049357326478</v>
       </c>
       <c r="D156" s="17" t="n">
-        <v>5.022782862039417</v>
+        <v>4.850174293059126</v>
       </c>
       <c r="E156" s="17" t="n">
-        <v>13.59129648671808</v>
+        <v>13.59444473007712</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4025,16 +4025,16 @@
         </is>
       </c>
       <c r="B157" s="17" t="n">
-        <v>2.46666940874036</v>
+        <v>2.51200411311054</v>
       </c>
       <c r="C157" s="17" t="n">
-        <v>2.800198457583547</v>
+        <v>2.863797686375321</v>
       </c>
       <c r="D157" s="17" t="n">
-        <v>3.334798457583548</v>
+        <v>3.220197686375321</v>
       </c>
       <c r="E157" s="17" t="n">
-        <v>8.601666323907455</v>
+        <v>8.595999485861181</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -4044,16 +4044,16 @@
         </is>
       </c>
       <c r="B158" s="17" t="n">
-        <v>3.304471324762437</v>
+        <v>3.372706987143656</v>
       </c>
       <c r="C158" s="17" t="n">
-        <v>3.379942761319173</v>
+        <v>3.452914141978759</v>
       </c>
       <c r="D158" s="17" t="n">
-        <v>4.026742761319174</v>
+        <v>3.88411414197876</v>
       </c>
       <c r="E158" s="17" t="n">
-        <v>10.71115684740078</v>
+        <v>10.70973527110117</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -4063,16 +4063,16 @@
         </is>
       </c>
       <c r="B159" s="17" t="n">
-        <v>4.956706987143655</v>
+        <v>5.059060480715483</v>
       </c>
       <c r="C159" s="17" t="n">
-        <v>5.035424930128563</v>
+        <v>5.144137395192845</v>
       </c>
       <c r="D159" s="17" t="n">
-        <v>5.999024930128565</v>
+        <v>5.786537395192846</v>
       </c>
       <c r="E159" s="17" t="n">
-        <v>15.99115684740078</v>
+        <v>15.98973527110117</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -4085,13 +4085,13 @@
         <v>0</v>
       </c>
       <c r="C160" s="17" t="n">
-        <v>0.5719121544537078</v>
+        <v>0.5856182316805617</v>
       </c>
       <c r="D160" s="17" t="n">
-        <v>0.6808121544537078</v>
+        <v>0.6582182316805618</v>
       </c>
       <c r="E160" s="17" t="n">
-        <v>1.252724308907416</v>
+        <v>1.243836463361124</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -4101,16 +4101,16 @@
         </is>
       </c>
       <c r="B161" s="17" t="n">
-        <v>4.136031533847472</v>
+        <v>4.212047300771208</v>
       </c>
       <c r="C161" s="17" t="n">
-        <v>4.484717395029991</v>
+        <v>4.586576092544987</v>
       </c>
       <c r="D161" s="17" t="n">
-        <v>5.340917395029991</v>
+        <v>5.157376092544987</v>
       </c>
       <c r="E161" s="17" t="n">
-        <v>13.96166632390745</v>
+        <v>13.95599948586118</v>
       </c>
     </row>
   </sheetData>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>22.27089552238806</v>
+        <v>22.28134328358209</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>20.42802307692308</v>
+        <v>20.46903461538461</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -4208,7 +4208,7 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>15.99115684740078</v>
+        <v>15.98973527110117</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>14.0216664326459</v>
+        <v>13.99649964896885</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>13.96166632390745</v>
+        <v>13.95599948586118</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="B11" s="17" t="n">
-        <v>13.59129648671808</v>
+        <v>13.59444473007712</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="B12" s="17" t="n">
-        <v>10.71115684740078</v>
+        <v>10.70973527110117</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>8.601666323907455</v>
+        <v>8.595999485861181</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>5.925966432645898</v>
+        <v>5.932699648968846</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>1.252724308907416</v>
+        <v>1.243836463361124</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1"/>
@@ -4322,10 +4322,10 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>22.27089552238806</v>
+        <v>22.28134328358209</v>
       </c>
       <c r="D19" s="17" t="n">
-        <v>22.27089552238806</v>
+        <v>22.28134328358209</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>20.42802307692308</v>
+        <v>20.46903461538461</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>22.27089552238806</v>
+        <v>22.28134328358209</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>15.99115684740078</v>
+        <v>15.98973527110117</v>
       </c>
       <c r="D21" s="17" t="n">
-        <v>15.99115684740078</v>
+        <v>15.98973527110117</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>13.96166632390745</v>
+        <v>13.95599948586118</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>15.99115684740078</v>
+        <v>15.98973527110117</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="C23" s="17" t="n">
-        <v>1.252724308907416</v>
+        <v>1.243836463361124</v>
       </c>
       <c r="D23" s="17" t="n">
-        <v>15.99115684740078</v>
+        <v>15.98973527110117</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>14.0216664326459</v>
+        <v>13.99649964896885</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>14.0216664326459</v>
+        <v>13.99649964896885</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>13.59129648671808</v>
+        <v>13.59444473007712</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>13.59129648671808</v>
+        <v>13.59444473007712</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>10.71115684740078</v>
+        <v>10.70973527110117</v>
       </c>
       <c r="D26" s="17" t="n">
-        <v>10.71115684740078</v>
+        <v>10.70973527110117</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>8.601666323907455</v>
+        <v>8.595999485861181</v>
       </c>
       <c r="D27" s="17" t="n">
-        <v>10.71115684740078</v>
+        <v>10.70973527110117</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -4466,10 +4466,10 @@
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>5.925966432645898</v>
+        <v>5.932699648968846</v>
       </c>
       <c r="D28" s="17" t="n">
-        <v>5.925966432645898</v>
+        <v>5.932699648968846</v>
       </c>
     </row>
   </sheetData>
